--- a/StructureDefinition-Signering-Deltagande-2.xlsx
+++ b/StructureDefinition-Signering-Deltagande-2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Signering-Deltagande-2.xlsx
+++ b/StructureDefinition-Signering-Deltagande-2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Signering : Deltagande).</t>
+    <t>Påförande av signatur.  
+Inom laboratoriedomänen finns det fyra olika typer av signering. Signeringen avser hela laboratoriesvaret eller enskilda analyser.
+1. Laboratoriesvaret signeras av en medicinskt ansvarig hälso- och sjukvårdspersonal på den ansvariga enheten.
+Den ansvariga enheten kan vara den remissvarsmottagande enheten eller den utförande enheten (exempelvis vid patientnära analyser).
+2. En enskild analys signeras av den hälso- och sjukvårdspersonal som utför analysen.
+3. Laboratoriesvaret signeras av hälso- och sjukvårdspersonal på den remissvarsmottagande enheten när det förs in i patientjournalen.
+4. En enskild analys signeras av hälso- och sjukvårdspersonal på den remissvarsmottagande enheten när den förs in i patientjournalen.</t>
   </si>
   <si>
     <t>Purpose</t>
